--- a/Stratig_TrvlBT.xlsx
+++ b/Stratig_TrvlBT.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Johnn\Documents\LinkedInPD\PowerBITables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{502C8D3F-324D-4AE9-9816-D4C31BE85CB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C886547-446F-433F-9F22-B9F985816340}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{68BA78B8-2C86-437C-938D-AB77866D1782}"/>
   </bookViews>
@@ -52,9 +52,6 @@
     <t>TRANSCOM-HQ</t>
   </si>
   <si>
-    <t>Carrier/Agency Code Travel Transit Entity</t>
-  </si>
-  <si>
     <t>AAL-T1-009 American Airlines Group</t>
   </si>
   <si>
@@ -64,9 +61,6 @@
     <t>Operational Sector</t>
   </si>
   <si>
-    <t>Primary Station Hub</t>
-  </si>
-  <si>
     <t>DAL-T1-007 Delta Air Lines Inc.</t>
   </si>
   <si>
@@ -107,6 +101,12 @@
   </si>
   <si>
     <t>SCHEDULE SECURE - FLIGHT COMPLIANCE PASS</t>
+  </si>
+  <si>
+    <t>Region</t>
+  </si>
+  <si>
+    <t>Commend Tier</t>
   </si>
 </sst>
 </file>
@@ -759,18 +759,6 @@
   </cellStyles>
   <dxfs count="11">
     <dxf>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
       <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
           <color indexed="64"/>
@@ -901,6 +889,15 @@
     </dxf>
     <dxf>
       <border outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
         <bottom style="thin">
           <color indexed="64"/>
         </bottom>
@@ -908,18 +905,21 @@
     </dxf>
     <dxf>
       <border outline="0">
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
           <color indexed="64"/>
         </left>
         <right style="thin">
           <color indexed="64"/>
         </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
+        <top/>
+        <bottom/>
       </border>
     </dxf>
   </dxfs>
@@ -936,16 +936,16 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{BAB850A6-2880-4939-94CA-25DDEFA28F06}" name="Table1" displayName="Table1" ref="A1:G10" totalsRowShown="0" headerRowDxfId="0" headerRowBorderDxfId="9" tableBorderDxfId="10" totalsRowBorderDxfId="8">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{BAB850A6-2880-4939-94CA-25DDEFA28F06}" name="Table1" displayName="Table1" ref="A1:G10" totalsRowShown="0" headerRowDxfId="10" headerRowBorderDxfId="9" tableBorderDxfId="8" totalsRowBorderDxfId="7">
   <autoFilter ref="A1:G10" xr:uid="{BAB850A6-2880-4939-94CA-25DDEFA28F06}"/>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{0C5F2614-86D9-4CE7-B371-29EAAA0F1742}" name="Carrier/Agency Code Travel Transit Entity" dataDxfId="7"/>
-    <tableColumn id="2" xr3:uid="{E27CC731-3189-4AF7-A4D1-3B9594F8DC04}" name="Operational Sector" dataDxfId="6"/>
-    <tableColumn id="3" xr3:uid="{FC941F08-8F06-4A47-B968-5660D8788069}" name="Primary Station Hub" dataDxfId="5"/>
-    <tableColumn id="4" xr3:uid="{FDFF86BD-7868-4809-BFC6-D79D4CEBDAF2}" name="Daily Dispatched Legs" dataDxfId="4"/>
-    <tableColumn id="5" xr3:uid="{25D7976C-F978-4EFB-BAB9-C6ED2C18CABC}" name="Disruption Delay Incidents" dataDxfId="3"/>
-    <tableColumn id="6" xr3:uid="{D9275B79-3E45-46DE-A8B1-27814605EBB1}" name="Disruption Intensity Index" dataDxfId="2"/>
-    <tableColumn id="7" xr3:uid="{AF2969C4-D443-485D-AD51-395C10B021E2}" name="Logistical Operational Assessment" dataDxfId="1"/>
+    <tableColumn id="1" xr3:uid="{0C5F2614-86D9-4CE7-B371-29EAAA0F1742}" name="Commend Tier" dataDxfId="6"/>
+    <tableColumn id="2" xr3:uid="{E27CC731-3189-4AF7-A4D1-3B9594F8DC04}" name="Operational Sector" dataDxfId="5"/>
+    <tableColumn id="3" xr3:uid="{FC941F08-8F06-4A47-B968-5660D8788069}" name="Region" dataDxfId="4"/>
+    <tableColumn id="4" xr3:uid="{FDFF86BD-7868-4809-BFC6-D79D4CEBDAF2}" name="Daily Dispatched Legs" dataDxfId="3"/>
+    <tableColumn id="5" xr3:uid="{25D7976C-F978-4EFB-BAB9-C6ED2C18CABC}" name="Disruption Delay Incidents" dataDxfId="2"/>
+    <tableColumn id="6" xr3:uid="{D9275B79-3E45-46DE-A8B1-27814605EBB1}" name="Disruption Intensity Index" dataDxfId="1"/>
+    <tableColumn id="7" xr3:uid="{AF2969C4-D443-485D-AD51-395C10B021E2}" name="Logistical Operational Assessment" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1282,30 +1282,30 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" s="4" t="s">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="D1" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="G1" s="6" t="s">
         <v>23</v>
-      </c>
-      <c r="F1" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="G1" s="6" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>0</v>
@@ -1323,12 +1323,12 @@
         <v>0</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>0</v>
@@ -1346,12 +1346,12 @@
         <v>0</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>0</v>
@@ -1369,12 +1369,12 @@
         <v>0</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>4</v>
@@ -1392,12 +1392,12 @@
         <v>0</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>4</v>
@@ -1415,12 +1415,12 @@
         <v>0</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>4</v>
@@ -1438,12 +1438,12 @@
         <v>0</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>7</v>
@@ -1461,12 +1461,12 @@
         <v>0</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>7</v>
@@ -1484,12 +1484,12 @@
         <v>0</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" s="7" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B10" s="8" t="s">
         <v>7</v>
@@ -1507,7 +1507,7 @@
         <v>0</v>
       </c>
       <c r="G10" s="9" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
   </sheetData>
